--- a/游戏设计王/老虎机数学专题-随机百搭.xlsx
+++ b/游戏设计王/老虎机数学专题-随机百搭.xlsx
@@ -353,13 +353,14 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
-  <numFmts count="6">
+  <numFmts count="7">
     <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="176" formatCode="0.0000%"/>
     <numFmt numFmtId="177" formatCode="0.00000000"/>
+    <numFmt numFmtId="178" formatCode="0.0000000000%"/>
   </numFmts>
   <fonts count="32">
     <font>
@@ -1058,7 +1059,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="44">
+  <cellXfs count="47">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -1143,6 +1144,9 @@
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="178" applyNumberFormat="1" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="178" applyNumberFormat="1" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="178" applyNumberFormat="1" fontId="2" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -5116,7 +5120,7 @@
       <c r="F27" s="4">
         <v>0</v>
       </c>
-      <c r="G27" s="9">
+      <c r="G27" s="44">
         <f t="shared" ref="G27:G58" si="0">((B$6+B27)*(C$6+C27)*(D$6+D27)*(E$4-E$6-E27)*(F$4-F$6-F27)*B$17+(B$6+B27)*(C$6+C27)*(D$6+D27)*(E$6+E27)*(F$4-F$6-F27)*C$17+(B$6+B27)*(C$6+C27)*(D$6+D27)*(E$6+E27)*(F$6+F27)*D$17+(B$7+B27)*(C$7+C27)*(D$7+D27)*(E$4-E$7-E27)*(F$4-F$7-F27)*B$18+(B$7+B27)*(C$7+C27)*(D$7+D27)*(E$7+E27)*(F$4-F$7-F27)*C$18+(B$7+B27)*(C$7+C27)*(D$7+D27)*(E$7+E27)*(F$7+F27)*D$18+(B$8+B27)*(C$8+C27)*(D$8+D27)*(E$4-E$8-E27)*(F$4-F$8-F27)*B$19+(B$8+B27)*(C$8+C27)*(D$8+D27)*(E$8+E27)*(F$4-F$8-F27)*C$19+(B$8+B27)*(C$8+C27)*(D$8+D27)*(E$8+E27)*(F$8+F27)*D$19+(B$9+B27)*(C$9+C27)*(D$9+D27)*(E$4-E$9-E27)*(F$4-F$9-F27)*B$20+(B$9+B27)*(C$9+C27)*(D$9+D27)*(E$9+E27)*(F$4-F$9-F27)*C$20+(B$9+B27)*(C$9+C27)*(D$9+D27)*(E$9+E27)*(F$9+F27)*D$20+(B$10+B27)*(C$10+C27)*(D$10+D27)*(E$4-E$10-E27)*(F$4-F$10-F27)*B$21+(B$10+B27)*(C$10+C27)*(D$10+D27)*(E$10+E27)*(F$4-F$10-F27)*C$21+(B$10+B27)*(C$10+C27)*(D$10+D27)*(E$10+E27)*(F$10+F27)*D$21)/PRODUCT($B$4:$F$4)</f>
         <v>0.20512</v>
       </c>
@@ -5173,7 +5177,7 @@
       <c r="F28" s="4">
         <v>0</v>
       </c>
-      <c r="G28" s="9">
+      <c r="G28" s="44">
         <f t="shared" si="0"/>
         <v>0.2564</v>
       </c>
@@ -5230,7 +5234,7 @@
       <c r="F29" s="4">
         <v>0</v>
       </c>
-      <c r="G29" s="9">
+      <c r="G29" s="44">
         <f t="shared" si="0"/>
         <v>0.2564</v>
       </c>
@@ -5287,7 +5291,7 @@
       <c r="F30" s="4">
         <v>0</v>
       </c>
-      <c r="G30" s="9">
+      <c r="G30" s="44">
         <f t="shared" si="0"/>
         <v>0.3205</v>
       </c>
@@ -5344,7 +5348,7 @@
       <c r="F31" s="4">
         <v>0</v>
       </c>
-      <c r="G31" s="9">
+      <c r="G31" s="44">
         <f t="shared" si="0"/>
         <v>0.2564</v>
       </c>
@@ -5401,7 +5405,7 @@
       <c r="F32" s="4">
         <v>0</v>
       </c>
-      <c r="G32" s="9">
+      <c r="G32" s="44">
         <f t="shared" si="0"/>
         <v>0.3205</v>
       </c>
@@ -5458,7 +5462,7 @@
       <c r="F33" s="4">
         <v>0</v>
       </c>
-      <c r="G33" s="9">
+      <c r="G33" s="44">
         <f t="shared" si="0"/>
         <v>0.3205</v>
       </c>
@@ -5515,7 +5519,7 @@
       <c r="F34" s="4">
         <v>0</v>
       </c>
-      <c r="G34" s="9">
+      <c r="G34" s="44">
         <f t="shared" si="0"/>
         <v>0.400625</v>
       </c>
@@ -5572,7 +5576,7 @@
       <c r="F35" s="4">
         <v>0</v>
       </c>
-      <c r="G35" s="9">
+      <c r="G35" s="44">
         <f t="shared" si="0"/>
         <v>0.2292</v>
       </c>
@@ -5629,7 +5633,7 @@
       <c r="F36" s="4">
         <v>0</v>
       </c>
-      <c r="G36" s="9">
+      <c r="G36" s="44">
         <f t="shared" si="0"/>
         <v>0.2865</v>
       </c>
@@ -5686,7 +5690,7 @@
       <c r="F37" s="4">
         <v>0</v>
       </c>
-      <c r="G37" s="9">
+      <c r="G37" s="44">
         <f t="shared" si="0"/>
         <v>0.2865</v>
       </c>
@@ -5743,7 +5747,7 @@
       <c r="F38" s="4">
         <v>0</v>
       </c>
-      <c r="G38" s="9">
+      <c r="G38" s="44">
         <f t="shared" si="0"/>
         <v>0.358125</v>
       </c>
@@ -5800,7 +5804,7 @@
       <c r="F39" s="4">
         <v>0</v>
       </c>
-      <c r="G39" s="9">
+      <c r="G39" s="44">
         <f t="shared" si="0"/>
         <v>0.2865</v>
       </c>
@@ -5857,7 +5861,7 @@
       <c r="F40" s="4">
         <v>0</v>
       </c>
-      <c r="G40" s="9">
+      <c r="G40" s="44">
         <f t="shared" si="0"/>
         <v>0.358125</v>
       </c>
@@ -5914,7 +5918,7 @@
       <c r="F41" s="4">
         <v>0</v>
       </c>
-      <c r="G41" s="9">
+      <c r="G41" s="44">
         <f t="shared" si="0"/>
         <v>0.358125</v>
       </c>
@@ -5971,7 +5975,7 @@
       <c r="F42" s="4">
         <v>0</v>
       </c>
-      <c r="G42" s="9">
+      <c r="G42" s="44">
         <f t="shared" si="0"/>
         <v>0.44765625</v>
       </c>
@@ -6028,7 +6032,7 @@
       <c r="F43" s="4">
         <v>1</v>
       </c>
-      <c r="G43" s="9">
+      <c r="G43" s="44">
         <f t="shared" si="0"/>
         <v>0.2088</v>
       </c>
@@ -6085,7 +6089,7 @@
       <c r="F44" s="4">
         <v>1</v>
       </c>
-      <c r="G44" s="9">
+      <c r="G44" s="44">
         <f t="shared" si="0"/>
         <v>0.261</v>
       </c>
@@ -6142,7 +6146,7 @@
       <c r="F45" s="4">
         <v>1</v>
       </c>
-      <c r="G45" s="9">
+      <c r="G45" s="44">
         <f t="shared" si="0"/>
         <v>0.261</v>
       </c>
@@ -6199,7 +6203,7 @@
       <c r="F46" s="4">
         <v>1</v>
       </c>
-      <c r="G46" s="9">
+      <c r="G46" s="44">
         <f t="shared" si="0"/>
         <v>0.32625</v>
       </c>
@@ -6256,7 +6260,7 @@
       <c r="F47" s="4">
         <v>1</v>
       </c>
-      <c r="G47" s="9">
+      <c r="G47" s="44">
         <f t="shared" si="0"/>
         <v>0.261</v>
       </c>
@@ -6313,7 +6317,7 @@
       <c r="F48" s="4">
         <v>1</v>
       </c>
-      <c r="G48" s="9">
+      <c r="G48" s="44">
         <f t="shared" si="0"/>
         <v>0.32625</v>
       </c>
@@ -6370,7 +6374,7 @@
       <c r="F49" s="4">
         <v>1</v>
       </c>
-      <c r="G49" s="9">
+      <c r="G49" s="44">
         <f t="shared" si="0"/>
         <v>0.32625</v>
       </c>
@@ -6427,7 +6431,7 @@
       <c r="F50" s="4">
         <v>1</v>
       </c>
-      <c r="G50" s="9">
+      <c r="G50" s="44">
         <f t="shared" si="0"/>
         <v>0.4078125</v>
       </c>
@@ -6484,7 +6488,7 @@
       <c r="F51" s="4">
         <v>1</v>
       </c>
-      <c r="G51" s="9">
+      <c r="G51" s="44">
         <f t="shared" si="0"/>
         <v>0.2355</v>
       </c>
@@ -6541,7 +6545,7 @@
       <c r="F52" s="4">
         <v>1</v>
       </c>
-      <c r="G52" s="9">
+      <c r="G52" s="44">
         <f t="shared" si="0"/>
         <v>0.294375</v>
       </c>
@@ -6598,7 +6602,7 @@
       <c r="F53" s="4">
         <v>1</v>
       </c>
-      <c r="G53" s="9">
+      <c r="G53" s="44">
         <f t="shared" si="0"/>
         <v>0.294375</v>
       </c>
@@ -6655,7 +6659,7 @@
       <c r="F54" s="4">
         <v>1</v>
       </c>
-      <c r="G54" s="9">
+      <c r="G54" s="44">
         <f t="shared" si="0"/>
         <v>0.36796875</v>
       </c>
@@ -6712,7 +6716,7 @@
       <c r="F55" s="4">
         <v>1</v>
       </c>
-      <c r="G55" s="9">
+      <c r="G55" s="44">
         <f t="shared" si="0"/>
         <v>0.294375</v>
       </c>
@@ -6769,7 +6773,7 @@
       <c r="F56" s="4">
         <v>1</v>
       </c>
-      <c r="G56" s="9">
+      <c r="G56" s="44">
         <f t="shared" si="0"/>
         <v>0.36796875</v>
       </c>
@@ -6826,7 +6830,7 @@
       <c r="F57" s="4">
         <v>1</v>
       </c>
-      <c r="G57" s="9">
+      <c r="G57" s="44">
         <f t="shared" si="0"/>
         <v>0.36796875</v>
       </c>
@@ -6883,7 +6887,7 @@
       <c r="F58" s="4">
         <v>1</v>
       </c>
-      <c r="G58" s="9">
+      <c r="G58" s="44">
         <f t="shared" si="0"/>
         <v>0.4599609375</v>
       </c>
@@ -9952,63 +9956,63 @@
       <c r="B103" s="12">
         <v>0</v>
       </c>
-      <c r="C103" s="12">
+      <c r="C103" s="45">
         <f t="shared" ref="C103:Q103" si="35">1/15</f>
         <v>0.0666666666666667</v>
       </c>
-      <c r="D103" s="12">
+      <c r="D103" s="45">
         <f t="shared" si="35"/>
         <v>0.0666666666666667</v>
       </c>
-      <c r="E103" s="12">
+      <c r="E103" s="45">
         <f t="shared" si="35"/>
         <v>0.0666666666666667</v>
       </c>
-      <c r="F103" s="12">
+      <c r="F103" s="45">
         <f t="shared" si="35"/>
         <v>0.0666666666666667</v>
       </c>
-      <c r="G103" s="12">
+      <c r="G103" s="45">
         <f t="shared" si="35"/>
         <v>0.0666666666666667</v>
       </c>
-      <c r="H103" s="12">
+      <c r="H103" s="45">
         <f t="shared" si="35"/>
         <v>0.0666666666666667</v>
       </c>
-      <c r="I103" s="12">
+      <c r="I103" s="45">
         <f t="shared" si="35"/>
         <v>0.0666666666666667</v>
       </c>
-      <c r="J103" s="12">
+      <c r="J103" s="45">
         <f t="shared" si="35"/>
         <v>0.0666666666666667</v>
       </c>
-      <c r="K103" s="12">
+      <c r="K103" s="45">
         <f t="shared" si="35"/>
         <v>0.0666666666666667</v>
       </c>
-      <c r="L103" s="12">
+      <c r="L103" s="45">
         <f t="shared" si="35"/>
         <v>0.0666666666666667</v>
       </c>
-      <c r="M103" s="12">
+      <c r="M103" s="45">
         <f t="shared" si="35"/>
         <v>0.0666666666666667</v>
       </c>
-      <c r="N103" s="12">
+      <c r="N103" s="45">
         <f t="shared" si="35"/>
         <v>0.0666666666666667</v>
       </c>
-      <c r="O103" s="12">
+      <c r="O103" s="45">
         <f t="shared" si="35"/>
         <v>0.0666666666666667</v>
       </c>
-      <c r="P103" s="12">
+      <c r="P103" s="45">
         <f t="shared" si="35"/>
         <v>0.0666666666666667</v>
       </c>
-      <c r="Q103" s="12">
+      <c r="Q103" s="45">
         <f t="shared" si="35"/>
         <v>0.0666666666666667</v>
       </c>
@@ -10020,67 +10024,67 @@
       <c r="A104" s="4" t="s">
         <v>92</v>
       </c>
-      <c r="B104" s="9">
+      <c r="B104" s="44">
         <f t="shared" ref="B104:Q104" si="36">SUMPRODUCT(C64:C95,$G$27:$G$58)</f>
         <v>0.20512</v>
       </c>
-      <c r="C104" s="9">
+      <c r="C104" s="44">
         <f t="shared" si="36"/>
         <v>0.217226666666667</v>
       </c>
-      <c r="D104" s="9">
+      <c r="D104" s="44">
         <f t="shared" si="36"/>
         <v>0.229922857142857</v>
       </c>
-      <c r="E104" s="9">
+      <c r="E104" s="44">
         <f t="shared" si="36"/>
         <v>0.243231373626374</v>
       </c>
-      <c r="F104" s="9">
+      <c r="F104" s="44">
         <f t="shared" si="36"/>
         <v>0.257175695970696</v>
       </c>
-      <c r="G104" s="9">
+      <c r="G104" s="44">
         <f t="shared" si="36"/>
         <v>0.271779995317183</v>
       </c>
-      <c r="H104" s="9">
+      <c r="H104" s="44">
         <f t="shared" si="36"/>
         <v>0.287069147727273</v>
       </c>
-      <c r="I104" s="9">
+      <c r="I104" s="44">
         <f t="shared" si="36"/>
         <v>0.303068747814685</v>
       </c>
-      <c r="J104" s="9">
+      <c r="J104" s="44">
         <f t="shared" si="36"/>
         <v>0.319805122377622</v>
       </c>
-      <c r="K104" s="9">
+      <c r="K104" s="44">
         <f t="shared" si="36"/>
         <v>0.337305344030969</v>
       </c>
-      <c r="L104" s="9">
+      <c r="L104" s="44">
         <f t="shared" si="36"/>
         <v>0.355597244838495</v>
       </c>
-      <c r="M104" s="9">
+      <c r="M104" s="44">
         <f t="shared" si="36"/>
         <v>0.374709429945055</v>
       </c>
-      <c r="N104" s="9">
+      <c r="N104" s="44">
         <f t="shared" si="36"/>
         <v>0.394671291208791</v>
       </c>
-      <c r="O104" s="9">
+      <c r="O104" s="44">
         <f t="shared" si="36"/>
         <v>0.415513020833333</v>
       </c>
-      <c r="P104" s="9">
+      <c r="P104" s="44">
         <f t="shared" si="36"/>
         <v>0.437265625</v>
       </c>
-      <c r="Q104" s="9">
+      <c r="Q104" s="44">
         <f t="shared" si="36"/>
         <v>0.4599609375</v>
       </c>
@@ -10148,7 +10152,7 @@
       <c r="A106" s="4" t="s">
         <v>93</v>
       </c>
-      <c r="B106" s="13">
+      <c r="B106" s="46">
         <f>SUM(B103:Q103)</f>
         <v>1</v>
       </c>
@@ -10205,7 +10209,7 @@
       <c r="A107" s="7" t="s">
         <v>94</v>
       </c>
-      <c r="B107" s="13">
+      <c r="B107" s="46">
         <f>SUMPRODUCT(B103:Q103,B104:Q104)</f>
         <v>0.3269535</v>
       </c>
